--- a/samples/R_科目余额表.xlsx
+++ b/samples/R_科目余额表.xlsx
@@ -442,7 +442,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -508,19 +508,19 @@
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>6000000</v>
+        <v>12000000</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1500000</v>
+        <v>2000000</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3500000</v>
+        <v>15000000</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>8000000</v>
+        <v>25000000</v>
       </c>
     </row>
     <row r="3">
@@ -531,26 +531,26 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>长期借款-建行(2027到期)</t>
+          <t>长期借款-工行渝北支行</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5000000</v>
+        <v>8000000</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>5000000</v>
+        <v>18000000</v>
       </c>
     </row>
     <row r="4">
@@ -561,26 +561,26 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>长期借款-工行(2028到期)</t>
+          <t>长期借款-建行两江支行</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1000000</v>
+        <v>4000000</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1500000</v>
+        <v>2000000</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3500000</v>
+        <v>5000000</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>3000000</v>
+        <v>7000000</v>
       </c>
     </row>
   </sheetData>

--- a/samples/R_科目余额表.xlsx
+++ b/samples/R_科目余额表.xlsx
@@ -442,7 +442,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
